--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>87.61747153856177</v>
+        <v>14.23783912501629</v>
       </c>
       <c r="D2" t="n">
-        <v>88.83819335753957</v>
+        <v>14.43620642060018</v>
       </c>
       <c r="E2" t="n">
-        <v>7.467566770962561</v>
+        <v>1.213479600281416</v>
       </c>
       <c r="F2" t="n">
-        <v>8.144392683757852</v>
+        <v>1.323463811110651</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.59462400386315</v>
+        <v>11.95912640062776</v>
       </c>
       <c r="D3" t="n">
-        <v>75.00439811450927</v>
+        <v>12.18821469360776</v>
       </c>
       <c r="E3" t="n">
-        <v>7.467566770962561</v>
+        <v>1.213479600281416</v>
       </c>
       <c r="F3" t="n">
-        <v>8.144392683757852</v>
+        <v>1.323463811110651</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>66.93896620098076</v>
+        <v>10.87758200765937</v>
       </c>
       <c r="D4" t="n">
-        <v>68.39894156653703</v>
+        <v>11.11482800456227</v>
       </c>
       <c r="E4" t="n">
-        <v>7.467566770962561</v>
+        <v>1.213479600281416</v>
       </c>
       <c r="F4" t="n">
-        <v>8.144392683757852</v>
+        <v>1.323463811110651</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.46533203583893</v>
+        <v>11.12561645582383</v>
       </c>
       <c r="D5" t="n">
-        <v>66.89169874990151</v>
+        <v>10.869901046859</v>
       </c>
       <c r="E5" t="n">
-        <v>7.467566770962561</v>
+        <v>1.213479600281416</v>
       </c>
       <c r="F5" t="n">
-        <v>8.144392683757852</v>
+        <v>1.323463811110651</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>70.14985942058523</v>
+        <v>11.3993521558451</v>
       </c>
       <c r="D6" t="n">
-        <v>68.55541239856778</v>
+        <v>11.14025451476727</v>
       </c>
       <c r="E6" t="n">
-        <v>7.467566770962561</v>
+        <v>1.213479600281416</v>
       </c>
       <c r="F6" t="n">
-        <v>8.144392683757852</v>
+        <v>1.323463811110651</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
